--- a/apps/api/data/excel_templates/subjects.xlsx
+++ b/apps/api/data/excel_templates/subjects.xlsx
@@ -530,7 +530,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:O1"/>
   <dataValidations count="2">
     <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">

--- a/apps/api/data/excel_templates/subjects.xlsx
+++ b/apps/api/data/excel_templates/subjects.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subjects" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'subjects'!$A$1:$O$1</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,10 +29,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -44,7 +41,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,16 +57,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -433,104 +433,104 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="3" min="1" max="4"/>
-    <col width="13" customWidth="1" style="3" min="2" max="2"/>
-    <col width="13" customWidth="1" style="3" min="3" max="3"/>
-    <col width="13" customWidth="1" style="3" min="4" max="4"/>
-    <col width="21" customWidth="1" style="3" min="5" max="5"/>
-    <col width="18" customWidth="1" style="3" min="6" max="9"/>
-    <col width="13" customWidth="1" style="3" min="7" max="7"/>
-    <col width="13" customWidth="1" style="3" min="8" max="8"/>
-    <col width="13" customWidth="1" style="3" min="9" max="9"/>
-    <col width="19" customWidth="1" style="3" min="10" max="10"/>
-    <col width="18" customWidth="1" style="3" min="11" max="15"/>
-    <col width="13" customWidth="1" style="3" min="12" max="12"/>
-    <col width="13" customWidth="1" style="3" min="13" max="13"/>
-    <col width="13" customWidth="1" style="3" min="14" max="14"/>
-    <col width="13" customWidth="1" style="3" min="15" max="15"/>
+    <col width="18" customWidth="1" style="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="2" max="2"/>
+    <col width="18" customWidth="1" style="1" min="3" max="3"/>
+    <col width="18" customWidth="1" style="1" min="4" max="4"/>
+    <col width="21" customWidth="1" style="1" min="5" max="5"/>
+    <col width="18" customWidth="1" style="1" min="6" max="6"/>
+    <col width="18" customWidth="1" style="1" min="7" max="7"/>
+    <col width="18" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18" customWidth="1" style="1" min="9" max="9"/>
+    <col width="19" customWidth="1" style="1" min="10" max="10"/>
+    <col width="18" customWidth="1" style="1" min="11" max="11"/>
+    <col width="18" customWidth="1" style="1" min="12" max="12"/>
+    <col width="18" customWidth="1" style="1" min="13" max="13"/>
+    <col width="18" customWidth="1" style="2" min="14" max="14"/>
+    <col width="18" customWidth="1" style="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>serial_number</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>short_description</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>competitors</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>vendors</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>fun_fact</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>organization_id</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>website_url</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>logo_url</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>metadata</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:O1"/>
   <dataValidations count="2">
     <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">

--- a/apps/api/data/excel_templates/subjects.xlsx
+++ b/apps/api/data/excel_templates/subjects.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -450,6 +450,7 @@
     <col width="18" customWidth="1" style="1" min="13" max="13"/>
     <col width="18" customWidth="1" style="2" min="14" max="14"/>
     <col width="18" customWidth="1" style="1" min="15" max="15"/>
+    <col width="18" customWidth="1" style="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,6 +527,11 @@
       <c r="O1" s="4" t="inlineStr">
         <is>
           <t>metadata</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>industries</t>
         </is>
       </c>
     </row>

--- a/apps/api/data/excel_templates/subjects.xlsx
+++ b/apps/api/data/excel_templates/subjects.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection lockStructure="1"/>
+  <workbookProtection workbookPassword="DB2D" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -536,7 +536,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
   <autoFilter ref="A1:O1"/>
   <dataValidations count="2">
     <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">

--- a/apps/api/data/excel_templates/subjects.xlsx
+++ b/apps/api/data/excel_templates/subjects.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="2" state="veryHidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'subjects'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'subjects'!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -537,7 +537,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:P1"/>
   <dataValidations count="2">
     <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
       <formula1>_lists!$A$2:$A$8</formula1>

--- a/apps/api/data/excel_templates/subjects.xlsx
+++ b/apps/api/data/excel_templates/subjects.xlsx
@@ -444,7 +444,7 @@
     <col width="18" customWidth="1" style="1" min="7" max="7"/>
     <col width="18" customWidth="1" style="1" min="8" max="8"/>
     <col width="18" customWidth="1" style="1" min="9" max="9"/>
-    <col width="19" customWidth="1" style="1" min="10" max="10"/>
+    <col width="21" customWidth="1" style="1" min="10" max="10"/>
     <col width="18" customWidth="1" style="1" min="11" max="11"/>
     <col width="18" customWidth="1" style="1" min="12" max="12"/>
     <col width="18" customWidth="1" style="1" min="13" max="13"/>
@@ -501,7 +501,7 @@
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>organization_id</t>
+          <t>organization_name</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
